--- a/outputs/Остатки с продажными ценами.xlsx
+++ b/outputs/Остатки с продажными ценами.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,9 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,6 +486,21 @@
           <t>Продажа х остаток, руб</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Продано за месяц, шт</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Выручка за месяц, руб</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -505,6 +523,15 @@
       <c r="F2" s="2" t="n">
         <v>43680</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>9754</v>
+      </c>
+      <c r="I2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -527,6 +554,15 @@
       <c r="F3" s="2" t="n">
         <v/>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -549,6 +585,15 @@
       <c r="F4" s="2" t="n">
         <v/>
       </c>
+      <c r="G4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -571,6 +616,15 @@
       <c r="F5" s="2" t="n">
         <v>87300</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>22731.28</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8.800000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -593,6 +647,15 @@
       <c r="F6" s="2" t="n">
         <v>1423960</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>709</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>396808.11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -615,6 +678,15 @@
       <c r="F7" s="2" t="n">
         <v>76024</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -637,6 +709,15 @@
       <c r="F8" s="2" t="n">
         <v>44000</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -659,6 +740,15 @@
       <c r="F9" s="2" t="n">
         <v>66000</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>718</v>
+      </c>
+      <c r="I9" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -681,6 +771,15 @@
       <c r="F10" s="2" t="n">
         <v>57200</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -703,6 +802,15 @@
       <c r="F11" s="2" t="n">
         <v>3159086</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>221457.44</v>
+      </c>
+      <c r="I11" t="n">
+        <v>36.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -725,6 +833,15 @@
       <c r="F12" s="2" t="n">
         <v>2366557</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>588438.75</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -747,6 +864,15 @@
       <c r="F13" s="2" t="n">
         <v>1415443</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>405701.45</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -769,6 +895,15 @@
       <c r="F14" s="2" t="n">
         <v>427500</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>186318.98</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -791,6 +926,15 @@
       <c r="F15" s="2" t="n">
         <v>297560</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>234412.91</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -813,6 +957,15 @@
       <c r="F16" s="2" t="n">
         <v>422569</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>91804.77</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -835,6 +988,15 @@
       <c r="F17" s="2" t="n">
         <v>1171235</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>190014.32</v>
+      </c>
+      <c r="I17" t="n">
+        <v>13.4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -857,6 +1019,15 @@
       <c r="F18" s="2" t="n">
         <v>1666161</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>124180.03</v>
+      </c>
+      <c r="I18" t="n">
+        <v>29.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -879,6 +1050,15 @@
       <c r="F19" s="2" t="n">
         <v>43524</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>40650.83</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -901,6 +1081,15 @@
       <c r="F20" s="2" t="n">
         <v>106600</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>87613.23</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -923,6 +1112,15 @@
       <c r="F21" s="2" t="n">
         <v>58200</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>9966</v>
+      </c>
+      <c r="I21" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -945,6 +1143,15 @@
       <c r="F22" s="2" t="n">
         <v>797968</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>115727</v>
+      </c>
+      <c r="I22" t="n">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -967,6 +1174,15 @@
       <c r="F23" s="2" t="n">
         <v>1813509</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>157888.47</v>
+      </c>
+      <c r="I23" t="n">
+        <v>27.2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -989,6 +1205,15 @@
       <c r="F24" s="2" t="n">
         <v>112000</v>
       </c>
+      <c r="G24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>56078.75</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1011,6 +1236,15 @@
       <c r="F25" s="2" t="n">
         <v>392202</v>
       </c>
+      <c r="G25" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30387.37</v>
+      </c>
+      <c r="I25" t="n">
+        <v>33.6</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1033,6 +1267,15 @@
       <c r="F26" s="2" t="n">
         <v/>
       </c>
+      <c r="G26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I26" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1055,6 +1298,15 @@
       <c r="F27" s="2" t="n">
         <v/>
       </c>
+      <c r="G27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I27" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1077,6 +1329,15 @@
       <c r="F28" s="2" t="n">
         <v/>
       </c>
+      <c r="G28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I28" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1099,6 +1360,15 @@
       <c r="F29" s="2" t="n">
         <v/>
       </c>
+      <c r="G29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I29" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1121,6 +1391,15 @@
       <c r="F30" s="2" t="n">
         <v/>
       </c>
+      <c r="G30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I30" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1143,6 +1422,15 @@
       <c r="F31" s="2" t="n">
         <v/>
       </c>
+      <c r="G31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I31" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1165,6 +1453,15 @@
       <c r="F32" s="2" t="n">
         <v/>
       </c>
+      <c r="G32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I32" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1187,6 +1484,15 @@
       <c r="F33" s="2" t="n">
         <v/>
       </c>
+      <c r="G33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I33" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1209,6 +1515,15 @@
       <c r="F34" s="2" t="n">
         <v/>
       </c>
+      <c r="G34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I34" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1231,6 +1546,15 @@
       <c r="F35" s="2" t="n">
         <v/>
       </c>
+      <c r="G35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I35" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1253,6 +1577,15 @@
       <c r="F36" s="2" t="n">
         <v/>
       </c>
+      <c r="G36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I36" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1275,6 +1608,15 @@
       <c r="F37" s="2" t="n">
         <v/>
       </c>
+      <c r="G37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I37" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1297,6 +1639,15 @@
       <c r="F38" s="2" t="n">
         <v/>
       </c>
+      <c r="G38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I38" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1319,6 +1670,15 @@
       <c r="F39" s="2" t="n">
         <v/>
       </c>
+      <c r="G39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I39" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1341,6 +1701,15 @@
       <c r="F40" s="2" t="n">
         <v/>
       </c>
+      <c r="G40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I40" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1363,6 +1732,15 @@
       <c r="F41" s="2" t="n">
         <v/>
       </c>
+      <c r="G41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I41" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1385,6 +1763,15 @@
       <c r="F42" s="2" t="n">
         <v>233600</v>
       </c>
+      <c r="G42" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>19555.25</v>
+      </c>
+      <c r="I42" t="n">
+        <v>34.8</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1407,6 +1794,15 @@
       <c r="F43" s="2" t="n">
         <v>233600</v>
       </c>
+      <c r="G43" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>28327.93</v>
+      </c>
+      <c r="I43" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1429,6 +1825,15 @@
       <c r="F44" s="2" t="n">
         <v>29200</v>
       </c>
+      <c r="G44" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>13093</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1451,6 +1856,15 @@
       <c r="F45" s="2" t="n">
         <v>45210</v>
       </c>
+      <c r="G45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I45" t="n">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1473,6 +1887,15 @@
       <c r="F46" s="2" t="n">
         <v>45210</v>
       </c>
+      <c r="G46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I46" t="n">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1495,6 +1918,15 @@
       <c r="F47" s="2" t="n">
         <v>45210</v>
       </c>
+      <c r="G47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I47" t="n">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1517,6 +1949,15 @@
       <c r="F48" s="2" t="n">
         <v/>
       </c>
+      <c r="G48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I48" t="n">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1539,6 +1980,15 @@
       <c r="F49" s="2" t="n">
         <v>59510</v>
       </c>
+      <c r="G49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I49" t="n">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1561,6 +2011,15 @@
       <c r="F50" s="2" t="n">
         <v/>
       </c>
+      <c r="G50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I50" t="n">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1583,6 +2042,15 @@
       <c r="F51" s="2" t="n">
         <v>59510</v>
       </c>
+      <c r="G51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I51" t="n">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1605,6 +2073,15 @@
       <c r="F52" s="2" t="n">
         <v>42130</v>
       </c>
+      <c r="G52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I52" t="n">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1627,6 +2104,15 @@
       <c r="F53" s="2" t="n">
         <v>59510</v>
       </c>
+      <c r="G53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I53" t="n">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1649,6 +2135,15 @@
       <c r="F54" s="2" t="n">
         <v>45210</v>
       </c>
+      <c r="G54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I54" t="n">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1671,6 +2166,15 @@
       <c r="F55" s="2" t="n">
         <v>462592</v>
       </c>
+      <c r="G55" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>94167</v>
+      </c>
+      <c r="I55" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1695,6 +2199,15 @@
       <c r="F56" s="2" t="n">
         <v>52000</v>
       </c>
+      <c r="G56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>3006</v>
+      </c>
+      <c r="I56" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1717,6 +2230,15 @@
       <c r="F57" s="2" t="n">
         <v>1463400</v>
       </c>
+      <c r="G57" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>175567.53</v>
+      </c>
+      <c r="I57" t="n">
+        <v>19.9</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1739,6 +2261,15 @@
       <c r="F58" s="2" t="n">
         <v>540408</v>
       </c>
+      <c r="G58" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>130897.79</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10.7</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1761,6 +2292,15 @@
       <c r="F59" s="2" t="n">
         <v>550992</v>
       </c>
+      <c r="G59" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>126725.61</v>
+      </c>
+      <c r="I59" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1783,6 +2323,15 @@
       <c r="F60" s="2" t="n">
         <v>75120</v>
       </c>
+      <c r="G60" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>77854.61</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1805,6 +2354,15 @@
       <c r="F61" s="2" t="n">
         <v>529100</v>
       </c>
+      <c r="G61" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>88119</v>
+      </c>
+      <c r="I61" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1827,6 +2385,15 @@
       <c r="F62" s="2" t="n">
         <v>734958</v>
       </c>
+      <c r="G62" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>15673</v>
+      </c>
+      <c r="I62" t="n">
+        <v>102.3</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1849,6 +2416,15 @@
       <c r="F63" s="2" t="n">
         <v>166680</v>
       </c>
+      <c r="G63" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I63" t="n">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1871,6 +2447,15 @@
       <c r="F64" s="2" t="n">
         <v>105300</v>
       </c>
+      <c r="G64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I64" t="n">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1893,6 +2478,15 @@
       <c r="F65" s="2" t="n">
         <v>77844</v>
       </c>
+      <c r="G65" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I65" t="n">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1915,6 +2509,15 @@
       <c r="F66" s="2" t="n">
         <v>63190</v>
       </c>
+      <c r="G66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I66" t="n">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1937,6 +2540,15 @@
       <c r="F67" s="2" t="n">
         <v>35928</v>
       </c>
+      <c r="G67" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>12180</v>
+      </c>
+      <c r="I67" t="n">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1959,6 +2571,15 @@
       <c r="F68" s="2" t="n">
         <v/>
       </c>
+      <c r="G68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I68" t="n">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1981,6 +2602,15 @@
       <c r="F69" s="2" t="n">
         <v/>
       </c>
+      <c r="G69" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>11360</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2003,6 +2633,15 @@
       <c r="F70" s="2" t="n">
         <v>68445</v>
       </c>
+      <c r="G70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I70" t="n">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2025,6 +2664,15 @@
       <c r="F71" s="2" t="n">
         <v>100656</v>
       </c>
+      <c r="G71" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>121979.66</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.8</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2047,6 +2695,15 @@
       <c r="F72" s="2" t="n">
         <v>179640</v>
       </c>
+      <c r="G72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I72" t="n">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2069,6 +2726,15 @@
       <c r="F73" s="2" t="n">
         <v>78912</v>
       </c>
+      <c r="G73" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>83137.60000000001</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2091,6 +2757,15 @@
       <c r="F74" s="2" t="n">
         <v>221940</v>
       </c>
+      <c r="G74" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>27237.59</v>
+      </c>
+      <c r="I74" t="n">
+        <v>19.3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2113,6 +2788,15 @@
       <c r="F75" s="2" t="n">
         <v/>
       </c>
+      <c r="G75" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>972</v>
+      </c>
+      <c r="I75" t="n">
+        <v>106.7</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2135,6 +2819,15 @@
       <c r="F76" s="2" t="n">
         <v/>
       </c>
+      <c r="G76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I76" t="n">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2157,6 +2850,15 @@
       <c r="F77" s="2" t="n">
         <v>350400</v>
       </c>
+      <c r="G77" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>131004.03</v>
+      </c>
+      <c r="I77" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2179,6 +2881,15 @@
       <c r="F78" s="2" t="n">
         <v>237510</v>
       </c>
+      <c r="G78" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>55459.05</v>
+      </c>
+      <c r="I78" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2201,6 +2912,15 @@
       <c r="F79" s="2" t="n">
         <v>53730</v>
       </c>
+      <c r="G79" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>47236.39</v>
+      </c>
+      <c r="I79" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2223,6 +2943,15 @@
       <c r="F80" s="2" t="n">
         <v>35940</v>
       </c>
+      <c r="G80" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>62911.86</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2245,6 +2974,15 @@
       <c r="F81" s="2" t="n">
         <v>86100</v>
       </c>
+      <c r="G81" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>29016.54</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2267,6 +3005,15 @@
       <c r="F82" s="2" t="n">
         <v>51660</v>
       </c>
+      <c r="G82" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>54387.84</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2289,6 +3036,15 @@
       <c r="F83" s="2" t="n">
         <v>3634260</v>
       </c>
+      <c r="G83" s="2" t="n">
+        <v>1369</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>1626187.49</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2311,6 +3067,15 @@
       <c r="F84" s="2" t="n">
         <v>311577</v>
       </c>
+      <c r="G84" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>52732.51</v>
+      </c>
+      <c r="I84" t="n">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2333,6 +3098,15 @@
       <c r="F85" s="2" t="n">
         <v>802008</v>
       </c>
+      <c r="G85" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>118335.02</v>
+      </c>
+      <c r="I85" t="n">
+        <v>14.8</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2355,6 +3129,15 @@
       <c r="F86" s="2" t="n">
         <v>28864</v>
       </c>
+      <c r="G86" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>19652</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2377,6 +3160,15 @@
       <c r="F87" s="2" t="n">
         <v>604716</v>
       </c>
+      <c r="G87" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>10513</v>
+      </c>
+      <c r="I87" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2401,6 +3193,15 @@
       <c r="F88" s="2" t="n">
         <v>13260</v>
       </c>
+      <c r="G88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2425,6 +3226,15 @@
       <c r="F89" s="2" t="n">
         <v>69795</v>
       </c>
+      <c r="G89" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>3804</v>
+      </c>
+      <c r="I89" t="n">
+        <v>27.5</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2449,6 +3259,15 @@
       <c r="F90" s="2" t="n">
         <v>31465</v>
       </c>
+      <c r="G90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2471,6 +3290,15 @@
       <c r="F91" s="2" t="n">
         <v>3304120</v>
       </c>
+      <c r="G91" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>2277797.19</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2493,6 +3321,15 @@
       <c r="F92" s="2" t="n">
         <v>6113492</v>
       </c>
+      <c r="G92" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>31620.82</v>
+      </c>
+      <c r="I92" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2515,6 +3352,15 @@
       <c r="F93" s="2" t="n">
         <v>2075704</v>
       </c>
+      <c r="G93" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>360930.18</v>
+      </c>
+      <c r="I93" t="n">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2537,6 +3383,15 @@
       <c r="F94" s="2" t="n">
         <v>117000</v>
       </c>
+      <c r="G94" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>12129.42</v>
+      </c>
+      <c r="I94" t="n">
+        <v>32.3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2559,6 +3414,15 @@
       <c r="F95" s="2" t="n">
         <v>8918</v>
       </c>
+      <c r="G95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>2056</v>
+      </c>
+      <c r="I95" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2581,6 +3445,15 @@
       <c r="F96" s="2" t="n">
         <v>85590</v>
       </c>
+      <c r="G96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>3779</v>
+      </c>
+      <c r="I96" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2603,6 +3476,15 @@
       <c r="F97" s="2" t="n">
         <v>1168500</v>
       </c>
+      <c r="G97" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>104641.28</v>
+      </c>
+      <c r="I97" t="n">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2625,6 +3507,15 @@
       <c r="F98" s="2" t="n">
         <v>47937</v>
       </c>
+      <c r="G98" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>7607.18</v>
+      </c>
+      <c r="I98" t="n">
+        <v>11.4</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2647,6 +3538,15 @@
       <c r="F99" s="2" t="n">
         <v>841500</v>
       </c>
+      <c r="G99" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>23949.69</v>
+      </c>
+      <c r="I99" t="n">
+        <v>80.90000000000001</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2669,6 +3569,15 @@
       <c r="F100" s="2" t="n">
         <v>52990</v>
       </c>
+      <c r="G100" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>8179.94</v>
+      </c>
+      <c r="I100" t="n">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2691,6 +3600,15 @@
       <c r="F101" s="2" t="n">
         <v>18216</v>
       </c>
+      <c r="G101" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>9154</v>
+      </c>
+      <c r="I101" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2713,6 +3631,15 @@
       <c r="F102" s="2" t="n">
         <v>1657787</v>
       </c>
+      <c r="G102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>5577</v>
+      </c>
+      <c r="I102" t="n">
+        <v>504.5</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2734,6 +3661,15 @@
       </c>
       <c r="F103" s="2" t="n">
         <v>472827</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -2751,6 +3687,13 @@
       <c r="F104" s="5" t="n">
         <v>44729149</v>
       </c>
+      <c r="G104" s="5" t="n">
+        <v>8441</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>9059166</v>
+      </c>
+      <c r="I104" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
